--- a/data/Report.xlsx
+++ b/data/Report.xlsx
@@ -1,41 +1,65 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://akalltruckingcom.sharepoint.com/sites/SSKTeam/Shared Documents/X - Sukhi Coding Docs/GithubStaticPages/NSTMS/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_DF293C1C772738DCD82B3B02D1BC2FAA59B98331" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{838214BF-1535-F147-A3D0-D6A6F55FA40F}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Start Odo</t>
+  </si>
+  <si>
+    <t>End Odo</t>
+  </si>
+  <si>
+    <t>Total Miles</t>
+  </si>
+  <si>
+    <t>2025-11-01</t>
+  </si>
+  <si>
+    <t>2025-11-02</t>
+  </si>
+  <si>
+    <t>2025-11-03</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>2025-11-05</t>
+  </si>
+  <si>
+    <t>2025-11-06</t>
+  </si>
+  <si>
+    <t>2025-11-07</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +89,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,40 +428,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="1" max="4" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Date</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Start Odo</v>
-      </c>
-      <c r="C1" t="str">
-        <v>End Odo</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Total Miles</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Missing Miles</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Notes</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2025-11-01</v>
+    <row r="1" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
       </c>
       <c r="B2">
         <v>57685</v>
@@ -440,16 +462,10 @@
       <c r="D2">
         <v>173</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2025-11-02</v>
+    </row>
+    <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>5</v>
       </c>
       <c r="B3">
         <v>57858</v>
@@ -460,16 +476,10 @@
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>2025-11-03</v>
+    </row>
+    <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>6</v>
       </c>
       <c r="B4">
         <v>57858</v>
@@ -480,16 +490,10 @@
       <c r="D4">
         <v>0</v>
       </c>
-      <c r="E4">
-        <v>428</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>2025-11-03</v>
+    </row>
+    <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5">
         <v>58286</v>
@@ -500,16 +504,10 @@
       <c r="D5">
         <v>638</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>2025-11-04</v>
+    </row>
+    <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6">
         <v>58924</v>
@@ -520,16 +518,10 @@
       <c r="D6">
         <v>143</v>
       </c>
-      <c r="E6">
-        <v>136</v>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>2025-11-04</v>
+    </row>
+    <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>7</v>
       </c>
       <c r="B7">
         <v>59203</v>
@@ -540,16 +532,10 @@
       <c r="D7">
         <v>384</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>2025-11-05</v>
+    </row>
+    <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>8</v>
       </c>
       <c r="B8">
         <v>59587</v>
@@ -560,16 +546,10 @@
       <c r="D8">
         <v>687</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>2025-11-06</v>
+    </row>
+    <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>9</v>
       </c>
       <c r="B9">
         <v>60274</v>
@@ -580,16 +560,10 @@
       <c r="D9">
         <v>0</v>
       </c>
-      <c r="E9">
-        <v>15</v>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>2025-11-06</v>
+    </row>
+    <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>9</v>
       </c>
       <c r="B10">
         <v>60289</v>
@@ -600,16 +574,10 @@
       <c r="D10">
         <v>692</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>2025-11-07</v>
+    </row>
+    <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>10</v>
       </c>
       <c r="B11">
         <v>60981</v>
@@ -620,16 +588,276 @@
       <c r="D11">
         <v>67</v>
       </c>
-      <c r="E11">
-        <v>134</v>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+    <ignoredError sqref="A1:D11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b68cd990-d56a-452e-9fdd-60b6b260bf42">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100074A8B429D10914EB972808481157EEE" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c3c8cf273a595f66c267356d70cd9999">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b68cd990-d56a-452e-9fdd-60b6b260bf42" xmlns:ns3="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2547ef2d6b21e04d17c9959592bdc173" ns2:_="" ns3:_="">
+    <xsd:import namespace="b68cd990-d56a-452e-9fdd-60b6b260bf42"/>
+    <xsd:import namespace="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b68cd990-d56a-452e-9fdd-60b6b260bf42" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2c8a02e2-3bc9-4581-b444-ddfa0db99db5" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="18" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="19" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{fde9fa41-776e-49e9-8caf-6b9126bc05a4}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56CB8A1E-8337-4098-8E99-9125D4D289E2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b68cd990-d56a-452e-9fdd-60b6b260bf42"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9AAEC9A-4D81-46BC-A3D8-2D8518059F12}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AC58DDE-BC2B-4C42-8F66-C452FD10B02A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b68cd990-d56a-452e-9fdd-60b6b260bf42"/>
+    <ds:schemaRef ds:uri="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/Report.xlsx
+++ b/data/Report.xlsx
@@ -397,239 +397,307 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H11"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Driver Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Truck</v>
+      </c>
+      <c r="C1" t="str">
         <v>Date</v>
       </c>
-      <c r="B1" t="str">
+      <c r="D1" t="str">
         <v>Start Odo</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>End Odo</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>Total Miles</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>Missing Miles</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>Notes</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>Driver A</v>
+      </c>
+      <c r="B2" t="str">
+        <v>MPL5046</v>
+      </c>
+      <c r="C2" t="str">
         <v>2025-11-01</v>
       </c>
-      <c r="B2">
+      <c r="D2">
         <v>57685</v>
       </c>
-      <c r="C2">
+      <c r="E2">
         <v>57858</v>
       </c>
-      <c r="D2">
+      <c r="F2">
         <v>173</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" t="str">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>Driver A</v>
+      </c>
+      <c r="B3" t="str">
+        <v>MPL5046</v>
+      </c>
+      <c r="C3" t="str">
         <v>2025-11-02</v>
       </c>
-      <c r="B3">
+      <c r="D3">
         <v>57858</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>57858</v>
       </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" t="str">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>Driver A</v>
+      </c>
+      <c r="B4" t="str">
+        <v>MPL5046</v>
+      </c>
+      <c r="C4" t="str">
         <v>2025-11-03</v>
       </c>
-      <c r="B4">
+      <c r="D4">
         <v>57858</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>57858</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>428</v>
       </c>
-      <c r="F4" t="str">
+      <c r="H4" t="str">
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>Driver A</v>
+      </c>
+      <c r="B5" t="str">
+        <v>MPL5046</v>
+      </c>
+      <c r="C5" t="str">
         <v>2025-11-03</v>
       </c>
-      <c r="B5">
+      <c r="D5">
         <v>58286</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>58924</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>638</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="str">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>Driver A</v>
+      </c>
+      <c r="B6" t="str">
+        <v>MPL5046</v>
+      </c>
+      <c r="C6" t="str">
         <v>2025-11-04</v>
       </c>
-      <c r="B6">
+      <c r="D6">
         <v>58924</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>59067</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>143</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>136</v>
       </c>
-      <c r="F6" t="str">
+      <c r="H6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>Driver A</v>
+      </c>
+      <c r="B7" t="str">
+        <v>MPL5046</v>
+      </c>
+      <c r="C7" t="str">
         <v>2025-11-04</v>
       </c>
-      <c r="B7">
+      <c r="D7">
         <v>59203</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>59587</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>384</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" t="str">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>Driver A</v>
+      </c>
+      <c r="B8" t="str">
+        <v>MPL5046</v>
+      </c>
+      <c r="C8" t="str">
         <v>2025-11-05</v>
       </c>
-      <c r="B8">
+      <c r="D8">
         <v>59587</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>60274</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>687</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="str">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="str">
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
+        <v>Driver A</v>
+      </c>
+      <c r="B9" t="str">
+        <v>MPL5046</v>
+      </c>
+      <c r="C9" t="str">
         <v>2025-11-06</v>
       </c>
-      <c r="B9">
+      <c r="D9">
         <v>60274</v>
       </c>
-      <c r="C9">
+      <c r="E9">
         <v>60274</v>
       </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
         <v>15</v>
       </c>
-      <c r="F9" t="str">
+      <c r="H9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>Driver A</v>
+      </c>
+      <c r="B10" t="str">
+        <v>MPL5046</v>
+      </c>
+      <c r="C10" t="str">
         <v>2025-11-06</v>
       </c>
-      <c r="B10">
+      <c r="D10">
         <v>60289</v>
       </c>
-      <c r="C10">
+      <c r="E10">
         <v>60981</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>692</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" t="str">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>Driver A</v>
+      </c>
+      <c r="B11" t="str">
+        <v>MPL5046</v>
+      </c>
+      <c r="C11" t="str">
         <v>2025-11-07</v>
       </c>
-      <c r="B11">
+      <c r="D11">
         <v>60981</v>
       </c>
-      <c r="C11">
+      <c r="E11">
         <v>61048</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <v>67</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>134</v>
       </c>
-      <c r="F11" t="str">
+      <c r="H11" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/Report.xlsx
+++ b/data/Report.xlsx
@@ -1,41 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://akalltruckingcom.sharepoint.com/sites/SSKTeam/Shared Documents/X - Sukhi Coding Docs/GithubStaticPages/NSTMS/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_49C77EB715E93ED45FE1AD30AD981FCE58B98F15" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AF352DC-FF1B-2F40-A443-F027AD5A49CD}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Driver Name</t>
+  </si>
+  <si>
+    <t>Truck</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Start Odo</t>
+  </si>
+  <si>
+    <t>End Odo</t>
+  </si>
+  <si>
+    <t>Total Miles</t>
+  </si>
+  <si>
+    <t>Missing Miles</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +80,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,313 +419,84 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="26" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="4" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Driver Name</v>
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" t="str">
-        <v>Truck</v>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" t="str">
-        <v>Date</v>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
-      <c r="D1" t="str">
-        <v>Start Odo</v>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
-      <c r="E1" t="str">
-        <v>End Odo</v>
+      <c r="E1" t="s">
+        <v>4</v>
       </c>
-      <c r="F1" t="str">
-        <v>Total Miles</v>
+      <c r="F1" t="s">
+        <v>5</v>
       </c>
-      <c r="G1" t="str">
-        <v>Missing Miles</v>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
-      <c r="H1" t="str">
-        <v>Notes</v>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Driver A</v>
-      </c>
-      <c r="B2" t="str">
-        <v>MPL5046</v>
-      </c>
-      <c r="C2" t="str">
-        <v>2025-11-01</v>
-      </c>
-      <c r="D2">
-        <v>57685</v>
-      </c>
-      <c r="E2">
-        <v>57858</v>
-      </c>
-      <c r="F2">
-        <v>173</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Driver A</v>
-      </c>
-      <c r="B3" t="str">
-        <v>MPL5046</v>
-      </c>
-      <c r="C3" t="str">
-        <v>2025-11-02</v>
-      </c>
-      <c r="D3">
-        <v>57858</v>
-      </c>
-      <c r="E3">
-        <v>57858</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Driver A</v>
-      </c>
-      <c r="B4" t="str">
-        <v>MPL5046</v>
-      </c>
-      <c r="C4" t="str">
-        <v>2025-11-03</v>
-      </c>
-      <c r="D4">
-        <v>57858</v>
-      </c>
-      <c r="E4">
-        <v>57858</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>428</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Driver A</v>
-      </c>
-      <c r="B5" t="str">
-        <v>MPL5046</v>
-      </c>
-      <c r="C5" t="str">
-        <v>2025-11-03</v>
-      </c>
-      <c r="D5">
-        <v>58286</v>
-      </c>
-      <c r="E5">
-        <v>58924</v>
-      </c>
-      <c r="F5">
-        <v>638</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Driver A</v>
-      </c>
-      <c r="B6" t="str">
-        <v>MPL5046</v>
-      </c>
-      <c r="C6" t="str">
-        <v>2025-11-04</v>
-      </c>
-      <c r="D6">
-        <v>58924</v>
-      </c>
-      <c r="E6">
-        <v>59067</v>
-      </c>
-      <c r="F6">
-        <v>143</v>
-      </c>
-      <c r="G6">
-        <v>136</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Driver A</v>
-      </c>
-      <c r="B7" t="str">
-        <v>MPL5046</v>
-      </c>
-      <c r="C7" t="str">
-        <v>2025-11-04</v>
-      </c>
-      <c r="D7">
-        <v>59203</v>
-      </c>
-      <c r="E7">
-        <v>59587</v>
-      </c>
-      <c r="F7">
-        <v>384</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Driver A</v>
-      </c>
-      <c r="B8" t="str">
-        <v>MPL5046</v>
-      </c>
-      <c r="C8" t="str">
-        <v>2025-11-05</v>
-      </c>
-      <c r="D8">
-        <v>59587</v>
-      </c>
-      <c r="E8">
-        <v>60274</v>
-      </c>
-      <c r="F8">
-        <v>687</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Driver A</v>
-      </c>
-      <c r="B9" t="str">
-        <v>MPL5046</v>
-      </c>
-      <c r="C9" t="str">
-        <v>2025-11-06</v>
-      </c>
-      <c r="D9">
-        <v>60274</v>
-      </c>
-      <c r="E9">
-        <v>60274</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>15</v>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Driver A</v>
-      </c>
-      <c r="B10" t="str">
-        <v>MPL5046</v>
-      </c>
-      <c r="C10" t="str">
-        <v>2025-11-06</v>
-      </c>
-      <c r="D10">
-        <v>60289</v>
-      </c>
-      <c r="E10">
-        <v>60981</v>
-      </c>
-      <c r="F10">
-        <v>692</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Driver A</v>
-      </c>
-      <c r="B11" t="str">
-        <v>MPL5046</v>
-      </c>
-      <c r="C11" t="str">
-        <v>2025-11-07</v>
-      </c>
-      <c r="D11">
-        <v>60981</v>
-      </c>
-      <c r="E11">
-        <v>61048</v>
-      </c>
-      <c r="F11">
-        <v>67</v>
-      </c>
-      <c r="G11">
-        <v>134</v>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError sqref="A1:H1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b68cd990-d56a-452e-9fdd-60b6b260bf42">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100074A8B429D10914EB972808481157EEE" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c3c8cf273a595f66c267356d70cd9999">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b68cd990-d56a-452e-9fdd-60b6b260bf42" xmlns:ns3="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2547ef2d6b21e04d17c9959592bdc173" ns2:_="" ns3:_="">
     <xsd:import namespace="b68cd990-d56a-452e-9fdd-60b6b260bf42"/>
@@ -903,34 +697,46 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b68cd990-d56a-452e-9fdd-60b6b260bf42">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E7733F0-F0DD-427D-A4B7-541CBEA41DC1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99E22787-D1E8-4E70-855D-8B59C042A09A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="b68cd990-d56a-452e-9fdd-60b6b260bf42"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A6213CE-7629-4E90-A844-CD3C0D48045B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A6213CE-7629-4E90-A844-CD3C0D48045B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99E22787-D1E8-4E70-855D-8B59C042A09A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E7733F0-F0DD-427D-A4B7-541CBEA41DC1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b68cd990-d56a-452e-9fdd-60b6b260bf42"/>
+    <ds:schemaRef ds:uri="9a7deb0a-ac1a-42e6-9673-f99d9f83ffc8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>